--- a/public/templates/sru-employees-import-template.xlsx
+++ b/public/templates/sru-employees-import-template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>نموذج استيراد بيانات الموظفين — نظام تقييم الأداء (جامعة سليمان الراجحي)</t>
   </si>
@@ -45,6 +45,9 @@
     <t>- هذا الملف لا يحتوي على بيانات الهيكل التنظيمي أو التسكين — لاستيراد ذلك استخدم النموذج المخصص في صفحة الهيكل التنظيمي.</t>
   </si>
   <si>
+    <t>الرقم الوظيفي للرئيس المباشر: اختياري. الرقم الوظيفي لرئيس الموظف المباشر كما في عمود EMPLOYEE NUMBER. الصف بلا رئيس، أو برئيس غير موجود، يُنشأ «بانتظار الاعتماد» ليُسند من شاشة الموظفين.</t>
+  </si>
+  <si>
     <t>Employee data import template — Performance Evaluation System (Sulaiman Alrajhi University)</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
     <t>- This file does not include organizational structure or staffing data — use the dedicated template on the Org Structure page for that.</t>
   </si>
   <si>
+    <t>الرقم الوظيفي للرئيس المباشر (line manager employee number): optional. The manager's EMPLOYEE NUMBER. A row without a manager, or whose manager is unknown, is created as pending so it can be placed from the Employees screen.</t>
+  </si>
+  <si>
     <t>EMPLOYEE NUMBER</t>
   </si>
   <si>
@@ -127,6 +133,9 @@
   </si>
   <si>
     <t>الدور في النظام</t>
+  </si>
+  <si>
+    <t>الرقم الوظيفي للرئيس المباشر</t>
   </si>
   <si>
     <t>90010</t>
@@ -596,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -657,15 +666,20 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -673,7 +687,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -683,12 +697,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -698,168 +712,177 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="19" width="22" customWidth="1"/>
+    <col min="20" max="20" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R2" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S2" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>